--- a/Data/DCOILBRENTEU.xlsx
+++ b/Data/DCOILBRENTEU.xlsx
@@ -32,7 +32,7 @@
     <t>This data may be copyrighted. Please refer to the Terms of Use: https://fred.stlouisfed.org/legal#fred-terms-faq</t>
   </si>
   <si>
-    <t>File Created: 2026-05-03 7:05 pm CDT</t>
+    <t>File Created: 2026-06-01 9:50 am CDT</t>
   </si>
   <si>
     <t>DCOILBRENTEU</t>
@@ -41,7 +41,7 @@
     <t>Crude Oil Prices: Brent - Europe, Dollars per Barrel, Daily, Not Seasonally Adjusted</t>
   </si>
   <si>
-    <t>Data Updated: 2026-04-29</t>
+    <t>Data Updated: 2026-05-28</t>
   </si>
   <si>
     <t>observation_date</t>
@@ -467,7 +467,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2147"/>
+  <dimension ref="A1:B2161"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.5703125" bestFit="1" customWidth="1"/>
@@ -17461,6 +17461,115 @@
         <v>113.89</v>
       </c>
     </row>
+    <row r="2148" spans="1:2">
+      <c r="A2148" s="4">
+        <v>46140</v>
+      </c>
+      <c r="B2148" s="2">
+        <v>117.62</v>
+      </c>
+    </row>
+    <row r="2149" spans="1:2">
+      <c r="A2149" s="4">
+        <v>46141</v>
+      </c>
+      <c r="B2149" s="2">
+        <v>124.16</v>
+      </c>
+    </row>
+    <row r="2150" spans="1:2">
+      <c r="A2150" s="4">
+        <v>46142</v>
+      </c>
+      <c r="B2150" s="2">
+        <v>124.24</v>
+      </c>
+    </row>
+    <row r="2151" spans="1:2">
+      <c r="A2151" s="4">
+        <v>46143</v>
+      </c>
+      <c r="B2151" s="2">
+        <v>118.26</v>
+      </c>
+    </row>
+    <row r="2152" spans="1:2">
+      <c r="A2152" s="4">
+        <v>46146</v>
+      </c>
+    </row>
+    <row r="2153" spans="1:2">
+      <c r="A2153" s="4">
+        <v>46147</v>
+      </c>
+      <c r="B2153" s="2">
+        <v>114.51</v>
+      </c>
+    </row>
+    <row r="2154" spans="1:2">
+      <c r="A2154" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B2154" s="2">
+        <v>103.7</v>
+      </c>
+    </row>
+    <row r="2155" spans="1:2">
+      <c r="A2155" s="4">
+        <v>46149</v>
+      </c>
+      <c r="B2155" s="2">
+        <v>101.82</v>
+      </c>
+    </row>
+    <row r="2156" spans="1:2">
+      <c r="A2156" s="4">
+        <v>46150</v>
+      </c>
+      <c r="B2156" s="2">
+        <v>103.48</v>
+      </c>
+    </row>
+    <row r="2157" spans="1:2">
+      <c r="A2157" s="4">
+        <v>46153</v>
+      </c>
+      <c r="B2157" s="2">
+        <v>106.11</v>
+      </c>
+    </row>
+    <row r="2158" spans="1:2">
+      <c r="A2158" s="4">
+        <v>46154</v>
+      </c>
+      <c r="B2158" s="2">
+        <v>111.37</v>
+      </c>
+    </row>
+    <row r="2159" spans="1:2">
+      <c r="A2159" s="4">
+        <v>46155</v>
+      </c>
+      <c r="B2159" s="2">
+        <v>110.28</v>
+      </c>
+    </row>
+    <row r="2160" spans="1:2">
+      <c r="A2160" s="4">
+        <v>46156</v>
+      </c>
+      <c r="B2160" s="2">
+        <v>110.91</v>
+      </c>
+    </row>
+    <row r="2161" spans="1:2">
+      <c r="A2161" s="4">
+        <v>46157</v>
+      </c>
+      <c r="B2161" s="2">
+        <v>113.96</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
